--- a/iter-v1.0.1-第二期/国内APP第二期测试用例.xlsx
+++ b/iter-v1.0.1-第二期/国内APP第二期测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12780"/>
+    <workbookView windowWidth="28800" windowHeight="12780" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="安卓" sheetId="1" r:id="rId1"/>
